--- a/survey_templates/039_productivity_and_wellness_survey--survey_templates.xlsx
+++ b/survey_templates/039_productivity_and_wellness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your average work hours last week?</t>
+          <t>Productivity And Wellness Survey What Is Your Average Work Hours Last Week Hint</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Do you feel supported?</t>
+          <t>Productivity And Wellness Survey Do You Feel Supported 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Do you feel connected at work?</t>
+          <t>Productivity And Wellness Survey Do You Feel Connected At Work 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Do you feel satisfied with your job?</t>
+          <t>Productivity And Wellness Survey Do You Feel Satisfied With Your Job 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Do you feel motivated?</t>
+          <t>Productivity And Wellness Survey Do You Feel Motivated 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member', 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Lead', 'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_40_hours',_'value':_1}</t>
+          <t>less_than_40_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 40 hours', 'value': 1}</t>
+          <t>Less than 40 hours</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'40_hours',_'value':_2}</t>
+          <t>40_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '40 hours', 'value': 2}</t>
+          <t>40 hours</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_40_hours',_'value':_3}</t>
+          <t>more_than_40_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 40 hours', 'value': 3}</t>
+          <t>More than 40 hours</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -1768,97 +1768,97 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_supported_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_supported_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often', 'value': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -2482,267 +2482,267 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_always',_'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Always', 'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_connected_at_work_2_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>productivity_and_wellness_survey_do_you_feel_motivated_choices</t>
+          <t>productivity_and_wellness_survey_do_you_feel_motivated_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_bit',_'value':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A bit', 'value': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat', 'value': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very',_'value':_'very'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very', 'value': 'Very'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely',_'value':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely', 'value': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
